--- a/data/source-momento4-planeacion-territorial/Experiencia_ _Transformaciones que nos conectan_. (UCUNDINAMARCA)(1-9).xlsx
+++ b/data/source-momento4-planeacion-territorial/Experiencia_ _Transformaciones que nos conectan_. (UCUNDINAMARCA)(1-9).xlsx
@@ -124,10 +124,10 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -176,10 +176,10 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -472,7 +472,7 @@
         <v>46265.483668981484</v>
       </c>
       <c r="D2" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I2" t="str">
         <v>Gestor del Conocimiento y el Aprendizaje</v>
@@ -495,7 +495,7 @@
         <v>46265.49092592593</v>
       </c>
       <c r="D3" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I3" t="str">
         <v>Gestor del Conocimiento y el Aprendizaje</v>
@@ -518,7 +518,7 @@
         <v>46265.494675925926</v>
       </c>
       <c r="D4" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I4" t="str">
         <v>Gestor del Conocimiento y el Aprendizaje</v>
@@ -541,7 +541,7 @@
         <v>46265.49675925926</v>
       </c>
       <c r="D5" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I5" t="str">
         <v>Creador de Oportunidades (estudiante)</v>
@@ -564,7 +564,7 @@
         <v>46265.50987268519</v>
       </c>
       <c r="D6" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I6" t="str">
         <v>Gestor del Conocimiento y el Aprendizaje</v>
@@ -587,7 +587,7 @@
         <v>46265.52636574074</v>
       </c>
       <c r="D7" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I7" t="str">
         <v>Gestor del Conocimiento y el Aprendizaje</v>
@@ -610,7 +610,7 @@
         <v>46265.52784722222</v>
       </c>
       <c r="D8" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I8" t="str">
         <v>Gestor del Conocimiento y el Aprendizaje</v>
@@ -633,7 +633,7 @@
         <v>46265.52790509259</v>
       </c>
       <c r="D9" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I9" t="str">
         <v>Gestor del Conocimiento y el Aprendizaje</v>
@@ -656,7 +656,7 @@
         <v>46265.613032407404</v>
       </c>
       <c r="D10" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I10" t="str">
         <v>Gestor del Conocimiento y el Aprendizaje</v>
